--- a/final_artifacts_in_paper_updated/01_main_results/ablation_feature_exclude.xlsx
+++ b/final_artifacts_in_paper_updated/01_main_results/ablation_feature_exclude.xlsx
@@ -474,7 +474,7 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Forecasting horizon (month lag)</t>
+          <t>Forecasting horizon</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
